--- a/corr_matrix/residual_exam4C_3PL.xlsx
+++ b/corr_matrix/residual_exam4C_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>4C02</t>
@@ -565,76 +570,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.205639543194226</v>
+        <v>-0.2054100025649886</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09989323323104946</v>
+        <v>0.1001714638016602</v>
       </c>
       <c r="E2" t="n">
-        <v>0.191270464553605</v>
+        <v>0.1913399498890223</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01232224490146876</v>
+        <v>0.01255245191193385</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1040583596777026</v>
+        <v>-0.1038494705736702</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1108277713636455</v>
+        <v>-0.1106352848649571</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1079708380092767</v>
+        <v>0.1079415680714916</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.057794468320073</v>
+        <v>-0.0576375741669767</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08171853227110734</v>
+        <v>0.08183795536450555</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.06483516006961992</v>
+        <v>-0.06470320348084993</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1739427029206624</v>
+        <v>-0.1736906611937875</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1595051857833306</v>
+        <v>-0.1594240268487866</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0155946653864001</v>
+        <v>-0.01558528409318326</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.06050944291259705</v>
+        <v>-0.06025216233895089</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.09229611290953836</v>
+        <v>-0.09224998874572861</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.008435647691230104</v>
+        <v>-0.008282372257091787</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1099393592129134</v>
+        <v>-0.1096715402491431</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05275985455131184</v>
+        <v>0.05281633063282301</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.06899215378430569</v>
+        <v>-0.06886692138681517</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2497331904516358</v>
+        <v>-0.2497818373938261</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.03609610089577297</v>
+        <v>-0.03593007392508196</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1090711350753841</v>
+        <v>-0.1091277153935969</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.08619089730852096</v>
+        <v>-0.08605117210947102</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.08887005473386682</v>
+        <v>0.08902700383944064</v>
       </c>
     </row>
     <row r="3">
@@ -644,79 +649,79 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.205639543194226</v>
+        <v>-0.2054100025649886</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2017453796403724</v>
+        <v>-0.2015884042915559</v>
       </c>
       <c r="E3" t="n">
-        <v>0.109294062485203</v>
+        <v>0.1092607884880213</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01496119694252765</v>
+        <v>0.01509708358407595</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1062200415953502</v>
+        <v>0.1061405893118799</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1064942134144553</v>
+        <v>0.1064172645674393</v>
       </c>
       <c r="I3" t="n">
-        <v>0.075295750277889</v>
+        <v>0.07527481081557393</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1482950246242323</v>
+        <v>-0.1485152310129524</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.01698078167600233</v>
+        <v>-0.01713492401025438</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1315061665201983</v>
+        <v>0.1314459080462539</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0792079545379766</v>
+        <v>0.07916086654408933</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1541655900236547</v>
+        <v>0.1540756741883477</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2851765212843844</v>
+        <v>-0.2855298030632076</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1052957670968108</v>
+        <v>-0.1053320247660428</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.00259726437915491</v>
+        <v>-0.002644862395630107</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1104820763083747</v>
+        <v>0.1107720591942073</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1054225989844731</v>
+        <v>-0.1052337186098929</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.03974232060633429</v>
+        <v>-0.03987673975086971</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01444777548706275</v>
+        <v>0.01430813878914821</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004246921385941589</v>
+        <v>0.003606276771926022</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2918728359673</v>
+        <v>-0.2919197559882994</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1391301071715389</v>
+        <v>-0.139477044620162</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.202192722114527</v>
+        <v>-0.2020494251346904</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.08247819890793236</v>
+        <v>-0.08257131505284818</v>
       </c>
     </row>
     <row r="4">
@@ -726,79 +731,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09989323323104946</v>
+        <v>0.1001714638016602</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2017453796403724</v>
+        <v>-0.2015884042915559</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03836530319854548</v>
+        <v>-0.03832927434008077</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0521461109955231</v>
+        <v>-0.0519178100859207</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006249328745143056</v>
+        <v>0.006329827749525682</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2053311280551838</v>
+        <v>-0.2052206962349315</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08477752759788408</v>
+        <v>0.08472231635928933</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2255389519008869</v>
+        <v>-0.2252878964094497</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.01559756545921888</v>
+        <v>-0.01558363460147743</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1199394491016759</v>
+        <v>-0.119890338550734</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1653019456546726</v>
+        <v>-0.1651707432787999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.07573266849051366</v>
+        <v>-0.07576013648479663</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1046758982916448</v>
+        <v>-0.1048212159665677</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.01699162789286175</v>
+        <v>-0.01685593667221405</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2290504599163902</v>
+        <v>-0.2290359807126941</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03803121092501166</v>
+        <v>0.03821744555058555</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1783518011128031</v>
+        <v>-0.1780676468105002</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005835388156302787</v>
+        <v>0.005797567310872284</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2372610620173846</v>
+        <v>0.2372418219446282</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.199072024706051</v>
+        <v>-0.1991722757839579</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07168007094762976</v>
+        <v>0.07179449692296166</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04991668391211933</v>
+        <v>0.04971448542820379</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01292970439118614</v>
+        <v>0.01305238654124091</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01175241885203644</v>
+        <v>0.01183035744128412</v>
       </c>
     </row>
     <row r="5">
@@ -808,79 +813,79 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.191270464553605</v>
+        <v>0.1913399498890223</v>
       </c>
       <c r="C5" t="n">
-        <v>0.109294062485203</v>
+        <v>0.1092607884880213</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.03836530319854548</v>
+        <v>-0.03832927434008077</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0166564942835407</v>
+        <v>-0.01641982479759958</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1826206864974501</v>
+        <v>0.1826496411247957</v>
       </c>
       <c r="H5" t="n">
-        <v>0.18061011229208</v>
+        <v>0.1806278535277964</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1028846518248787</v>
+        <v>-0.1030318077955681</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1045354590516148</v>
+        <v>0.1045532321386426</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1478346986280036</v>
+        <v>-0.1478731904024399</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.04853795533404766</v>
+        <v>-0.0484006205065781</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0029557669921599</v>
+        <v>0.00306436695066677</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1200164019172613</v>
+        <v>-0.1200732088160778</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2898680330599693</v>
+        <v>-0.2900525670863465</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01897385604382755</v>
+        <v>-0.01870783634151672</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2370600078840905</v>
+        <v>-0.2371891918293908</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06307329270376287</v>
+        <v>0.06304620136505577</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1084445375635542</v>
+        <v>-0.1082296766706399</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1373159993283392</v>
+        <v>-0.1374622607875093</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1456343934665265</v>
+        <v>0.145607480166091</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1467850101407392</v>
+        <v>-0.1470353716451896</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1800348144684367</v>
+        <v>-0.1801279545630484</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1671956975777919</v>
+        <v>0.1669845237159357</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1482396919697317</v>
+        <v>-0.1481410871798134</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1762175828669527</v>
+        <v>-0.1763710927566982</v>
       </c>
     </row>
     <row r="6">
@@ -890,79 +895,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01232224490146876</v>
+        <v>0.01255245191193385</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01496119694252765</v>
+        <v>0.01509708358407595</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0521461109955231</v>
+        <v>-0.0519178100859207</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0166564942835407</v>
+        <v>-0.01641982479759958</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.07201546153603057</v>
+        <v>-0.07182192496110974</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1642839144051399</v>
+        <v>0.1644109059397666</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08880513725059772</v>
+        <v>-0.08887212228697162</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1483834739049352</v>
+        <v>-0.1482277383439377</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1025735292128262</v>
+        <v>-0.1024699063301782</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.01676035057287913</v>
+        <v>-0.01651001517487244</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1561813161431365</v>
+        <v>-0.1559159827112167</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2324034385490907</v>
+        <v>0.2324840722126263</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.05196076757485566</v>
+        <v>-0.05203428753936466</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0220154638265169</v>
+        <v>0.02238727449206816</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01166121713375814</v>
+        <v>0.01160623807879198</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1239776190046461</v>
+        <v>-0.1238802224644606</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1135929484735063</v>
+        <v>0.1138170852663261</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2627726131735462</v>
+        <v>0.2628065100181004</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1038252833343932</v>
+        <v>-0.1037206975247468</v>
       </c>
       <c r="V6" t="n">
-        <v>0.07778865401586069</v>
+        <v>0.07772040980555681</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1314658902774542</v>
+        <v>-0.1314095280503499</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.08532098464272159</v>
+        <v>-0.08545690892035933</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.09580606191283773</v>
+        <v>-0.09564656721368495</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1356286229025384</v>
+        <v>-0.1355731716879831</v>
       </c>
     </row>
     <row r="7">
@@ -972,79 +977,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1040583596777026</v>
+        <v>-0.1038494705736702</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1062200415953502</v>
+        <v>0.1061405893118799</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006249328745143056</v>
+        <v>0.006329827749525682</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1826206864974501</v>
+        <v>0.1826496411247957</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.07201546153603057</v>
+        <v>-0.07182192496110974</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06158627069359457</v>
+        <v>-0.06151147079007632</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1796257232978683</v>
+        <v>-0.179697544466537</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009737435715951896</v>
+        <v>0.00977367084204832</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2806750704769231</v>
+        <v>-0.2806571144074686</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1102688926707943</v>
+        <v>0.1103069459290895</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06614051860030794</v>
+        <v>0.06621424067595873</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01343879421327011</v>
+        <v>-0.01348813658105069</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04520452949948815</v>
+        <v>0.04511535002117396</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.08232284951271147</v>
+        <v>-0.08210266408615639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1302022701901307</v>
+        <v>-0.1302699230529848</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.01508649441504894</v>
+        <v>-0.01498647469971973</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.08425234243548027</v>
+        <v>-0.08402961110812916</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2616675098037464</v>
+        <v>-0.2617800037487998</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2298892423020111</v>
+        <v>0.2298962810852762</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1121858428987182</v>
+        <v>-0.1124404061729649</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1346242616124491</v>
+        <v>-0.1345922733239165</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1195664543163452</v>
+        <v>0.1193872172447245</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.2820732308707531</v>
+        <v>-0.2819706479157542</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.0762132241433276</v>
+        <v>-0.076194565823632</v>
       </c>
     </row>
     <row r="8">
@@ -1054,79 +1059,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1108277713636455</v>
+        <v>-0.1106352848649571</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1064942134144553</v>
+        <v>0.1064172645674393</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2053311280551838</v>
+        <v>-0.2052206962349315</v>
       </c>
       <c r="E8" t="n">
-        <v>0.18061011229208</v>
+        <v>0.1806278535277964</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1642839144051399</v>
+        <v>0.1644109059397666</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.06158627069359457</v>
+        <v>-0.06151147079007632</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.183645235714591</v>
+        <v>-0.1837285891935166</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.09680579139974453</v>
+        <v>-0.09675928811893318</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2921192954265392</v>
+        <v>-0.2921369235081319</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1441643070670473</v>
+        <v>-0.1441206728911062</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1687747399172436</v>
+        <v>-0.1687041643547087</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.01975795664911972</v>
+        <v>-0.01983435641876129</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2472976498671366</v>
+        <v>-0.2474257462969509</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.08852486899362545</v>
+        <v>-0.08832644599112857</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1506692403582256</v>
+        <v>0.1505886103787175</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1148889428773899</v>
+        <v>0.1149626442191978</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.09453958322058627</v>
+        <v>-0.09433269685077221</v>
       </c>
       <c r="T8" t="n">
-        <v>0.006579521704376482</v>
+        <v>0.006483902477425836</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04820173804353547</v>
+        <v>0.04818628998717302</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0002515138532249115</v>
+        <v>-0.0004700889859805831</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2074226366947533</v>
+        <v>0.207420181396017</v>
       </c>
       <c r="X8" t="n">
-        <v>0.111124016508586</v>
+        <v>0.1109223096010071</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.03099954659904147</v>
+        <v>-0.03093110006872712</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.08442215372258249</v>
+        <v>-0.0844352615849611</v>
       </c>
     </row>
     <row r="9">
@@ -1136,79 +1141,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1079708380092767</v>
+        <v>0.1079415680714916</v>
       </c>
       <c r="C9" t="n">
-        <v>0.075295750277889</v>
+        <v>0.07527481081557393</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08477752759788408</v>
+        <v>0.08472231635928933</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1028846518248787</v>
+        <v>-0.1030318077955681</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08880513725059772</v>
+        <v>-0.08887212228697162</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1796257232978683</v>
+        <v>-0.179697544466537</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.183645235714591</v>
+        <v>-0.1837285891935166</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07424994587596845</v>
+        <v>0.07425152621335214</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2629406876596865</v>
+        <v>0.2628668176106725</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1150232336639299</v>
+        <v>-0.1151415139960121</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.170114703872529</v>
+        <v>-0.1701337722478113</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4147395023734399</v>
+        <v>0.4146329794359667</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08234377920679431</v>
+        <v>0.08222642267162036</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.09328381148726991</v>
+        <v>-0.09330923147947447</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.248639424163533</v>
+        <v>-0.2487714727323843</v>
       </c>
       <c r="R9" t="n">
-        <v>0.147933598397444</v>
+        <v>0.1478805327113187</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1387276208899552</v>
+        <v>-0.1386805205858133</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5030065483139712</v>
+        <v>0.5028918980575215</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2040858827077455</v>
+        <v>-0.2041843373497768</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0301381636938453</v>
+        <v>0.03006124644510077</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2294846313766877</v>
+        <v>-0.2296271658011686</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2888588128617268</v>
+        <v>-0.2891012929506928</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1720368923075383</v>
+        <v>-0.1720480937019976</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.326143800154486</v>
+        <v>0.3259749648975535</v>
       </c>
     </row>
     <row r="10">
@@ -1218,79 +1223,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.057794468320073</v>
+        <v>-0.0576375741669767</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1482950246242323</v>
+        <v>-0.1485152310129524</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2255389519008869</v>
+        <v>-0.2252878964094497</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1045354590516148</v>
+        <v>0.1045532321386426</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1483834739049352</v>
+        <v>-0.1482277383439377</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009737435715951896</v>
+        <v>0.00977367084204832</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.09680579139974453</v>
+        <v>-0.09675928811893318</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07424994587596845</v>
+        <v>0.07425152621335214</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1033712343917588</v>
+        <v>-0.1033438792546884</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.01970292189816571</v>
+        <v>-0.01966653980693922</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1727819404802736</v>
+        <v>0.1728590192193444</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1198067131128524</v>
+        <v>-0.1197801791357047</v>
       </c>
       <c r="O10" t="n">
-        <v>0.009472582974583631</v>
+        <v>0.009369406636192035</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02512093382197651</v>
+        <v>0.02516544464309807</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1606194040448648</v>
+        <v>-0.1606085487321036</v>
       </c>
       <c r="R10" t="n">
-        <v>0.007713302303347485</v>
+        <v>0.008053252466191858</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1063450937332363</v>
+        <v>0.1064627469181827</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1889990524636923</v>
+        <v>-0.1889946715056594</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.06602709281384164</v>
+        <v>-0.06600846246255264</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1309218495581397</v>
+        <v>-0.1312299214321575</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.2668837030410903</v>
+        <v>-0.2667814048004511</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1979854045222275</v>
+        <v>-0.1981196967950597</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.04218775799190306</v>
+        <v>-0.04200067933560697</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.06544180406989297</v>
+        <v>0.06551259929629835</v>
       </c>
     </row>
     <row r="11">
@@ -1300,79 +1305,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08171853227110734</v>
+        <v>0.08183795536450555</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.01698078167600233</v>
+        <v>-0.01713492401025438</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.01559756545921888</v>
+        <v>-0.01558363460147743</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1478346986280036</v>
+        <v>-0.1478731904024399</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1025735292128262</v>
+        <v>-0.1024699063301782</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2806750704769231</v>
+        <v>-0.2806571144074686</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2921192954265392</v>
+        <v>-0.2921369235081319</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2629406876596865</v>
+        <v>0.2628668176106725</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1033712343917588</v>
+        <v>-0.1033438792546884</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08663382046753906</v>
+        <v>0.08658479623333339</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1561794088156516</v>
+        <v>0.1561858135919647</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.04950909852705745</v>
+        <v>-0.04967848019660998</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1455913195659315</v>
+        <v>0.1454501897385892</v>
       </c>
       <c r="P11" t="n">
-        <v>0.09875267801190611</v>
+        <v>0.09884650069562316</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.3373929604986302</v>
+        <v>-0.3375463480306599</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.0615513167349947</v>
+        <v>-0.06149676501353601</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1298613853834337</v>
+        <v>-0.1296773898151519</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.01912205896620874</v>
+        <v>-0.01931290046390944</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1663619096213954</v>
+        <v>-0.1664411450377694</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1119572119076825</v>
+        <v>0.1117532079143059</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.004700357538873538</v>
+        <v>-0.004751986596468862</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.06894626734859351</v>
+        <v>-0.06924541095982775</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.07019380674236816</v>
+        <v>0.07023693466241687</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.1205309805052715</v>
+        <v>-0.1206372420352425</v>
       </c>
     </row>
     <row r="12">
@@ -1382,79 +1387,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.06483516006961992</v>
+        <v>-0.06470320348084993</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1315061665201983</v>
+        <v>0.1314459080462539</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1199394491016759</v>
+        <v>-0.119890338550734</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04853795533404766</v>
+        <v>-0.0484006205065781</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.01676035057287913</v>
+        <v>-0.01651001517487244</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1102688926707943</v>
+        <v>0.1103069459290895</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1441643070670473</v>
+        <v>-0.1441206728911062</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1150232336639299</v>
+        <v>-0.1151415139960121</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.01970292189816571</v>
+        <v>-0.01966653980693922</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08663382046753906</v>
+        <v>0.08658479623333339</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2413452860392148</v>
+        <v>0.2414071550629436</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1391878669541757</v>
+        <v>-0.1392416425355656</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2439507968159924</v>
+        <v>0.2437738839263515</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.02048501507770963</v>
+        <v>-0.02021263180460268</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.07935677426868894</v>
+        <v>-0.0794935523760925</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.2079473370306356</v>
+        <v>-0.2079328079425145</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1328373091667853</v>
+        <v>-0.1326199575791063</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1571888366462373</v>
+        <v>-0.1573142788404364</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06607480655853307</v>
+        <v>0.06603910002484312</v>
       </c>
       <c r="V12" t="n">
-        <v>0.05859633738897414</v>
+        <v>0.05839299594341828</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.20804940814984</v>
+        <v>-0.2081303098943921</v>
       </c>
       <c r="X12" t="n">
-        <v>0.008982313006026133</v>
+        <v>0.00872265517362595</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.1816849017478241</v>
+        <v>-0.1815966141572318</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.1984844848751004</v>
+        <v>-0.1986007863816881</v>
       </c>
     </row>
     <row r="13">
@@ -1464,79 +1469,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1739427029206624</v>
+        <v>-0.1736906611937875</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0792079545379766</v>
+        <v>0.07916086654408933</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1653019456546726</v>
+        <v>-0.1651707432787999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0029557669921599</v>
+        <v>0.00306436695066677</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1561813161431365</v>
+        <v>-0.1559159827112167</v>
       </c>
       <c r="G13" t="n">
-        <v>0.06614051860030794</v>
+        <v>0.06621424067595873</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1687747399172436</v>
+        <v>-0.1687041643547087</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.170114703872529</v>
+        <v>-0.1701337722478113</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1727819404802736</v>
+        <v>0.1728590192193444</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1561794088156516</v>
+        <v>0.1561858135919647</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2413452860392148</v>
+        <v>0.2414071550629436</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1890440118055939</v>
+        <v>-0.1890623138121295</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02282422551711334</v>
+        <v>0.02271304277037642</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04482032185244989</v>
+        <v>0.04499624628803417</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2090905507869948</v>
+        <v>-0.2091357058975058</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.09474841304816356</v>
+        <v>-0.09463613250876128</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.05847751416331348</v>
+        <v>-0.05825850648067452</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3071277002230445</v>
+        <v>-0.3071695651052038</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1338208307639991</v>
+        <v>-0.133827675350275</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.09372874860603495</v>
+        <v>-0.09393684307138966</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.09646348322619602</v>
+        <v>-0.09640080403981131</v>
       </c>
       <c r="X13" t="n">
-        <v>0.00480595699651474</v>
+        <v>0.004603166181255202</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.1089591576588941</v>
+        <v>-0.1088783445811544</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.220650463279321</v>
+        <v>-0.220593990499291</v>
       </c>
     </row>
     <row r="14">
@@ -1546,79 +1551,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1595051857833306</v>
+        <v>-0.1594240268487866</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1541655900236547</v>
+        <v>0.1540756741883477</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.07573266849051366</v>
+        <v>-0.07576013648479663</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1200164019172613</v>
+        <v>-0.1200732088160778</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2324034385490907</v>
+        <v>0.2324840722126263</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.01343879421327011</v>
+        <v>-0.01348813658105069</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.01975795664911972</v>
+        <v>-0.01983435641876129</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4147395023734399</v>
+        <v>0.4146329794359667</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1198067131128524</v>
+        <v>-0.1197801791357047</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.04950909852705745</v>
+        <v>-0.04967848019660998</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1391878669541757</v>
+        <v>-0.1392416425355656</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1890440118055939</v>
+        <v>-0.1890623138121295</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06899175936116179</v>
+        <v>0.06874183305208487</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0969912360908857</v>
+        <v>-0.09685945936205609</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1614593559348005</v>
+        <v>0.1612837181202157</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1341805013091428</v>
+        <v>-0.1342267186319498</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.06156876208388055</v>
+        <v>-0.06140207725824862</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4662533462034805</v>
+        <v>0.4661020457396655</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.07012080581278801</v>
+        <v>-0.07026386430840173</v>
       </c>
       <c r="V14" t="n">
-        <v>0.07201465038179668</v>
+        <v>0.07178292317710309</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3327715338028381</v>
+        <v>-0.3329886446960995</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02586050107867468</v>
+        <v>0.02549074894260714</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.1154139003323497</v>
+        <v>-0.115403743209584</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.02449975751638415</v>
+        <v>-0.02475705210275715</v>
       </c>
     </row>
     <row r="15">
@@ -1628,79 +1633,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0155946653864001</v>
+        <v>-0.01558528409318326</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2851765212843844</v>
+        <v>-0.2855298030632076</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1046758982916448</v>
+        <v>-0.1048212159665677</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2898680330599693</v>
+        <v>-0.2900525670863465</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05196076757485566</v>
+        <v>-0.05203428753936466</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04520452949948815</v>
+        <v>0.04511535002117396</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2472976498671366</v>
+        <v>-0.2474257462969509</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08234377920679431</v>
+        <v>0.08222642267162036</v>
       </c>
       <c r="J15" t="n">
-        <v>0.009472582974583631</v>
+        <v>0.009369406636192035</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1455913195659315</v>
+        <v>0.1454501897385892</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2439507968159924</v>
+        <v>0.2437738839263515</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02282422551711334</v>
+        <v>0.02271304277037642</v>
       </c>
       <c r="N15" t="n">
-        <v>0.06899175936116179</v>
+        <v>0.06874183305208487</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.02442690568377385</v>
+        <v>0.02436793672088812</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1310600885132061</v>
+        <v>-0.1312150757848662</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.2505971458399764</v>
+        <v>-0.2506507994936982</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1386911605195124</v>
+        <v>-0.1386052563586558</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1938716374911583</v>
+        <v>0.1936456512416965</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.06292308932809113</v>
+        <v>-0.06307131369245933</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01119262976974705</v>
+        <v>0.01088845802165236</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.1742537132925413</v>
+        <v>-0.1743977761574571</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2133304784340256</v>
+        <v>0.2131093137364903</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.117410069678652</v>
+        <v>-0.1174551260344697</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.001705873514255443</v>
+        <v>0.001503559656886216</v>
       </c>
     </row>
     <row r="16">
@@ -1710,79 +1715,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.06050944291259705</v>
+        <v>-0.06025216233895089</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1052957670968108</v>
+        <v>-0.1053320247660428</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.01699162789286175</v>
+        <v>-0.01685593667221405</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01897385604382755</v>
+        <v>-0.01870783634151672</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0220154638265169</v>
+        <v>0.02238727449206816</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.08232284951271147</v>
+        <v>-0.08210266408615639</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.08852486899362545</v>
+        <v>-0.08832644599112857</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.09328381148726991</v>
+        <v>-0.09330923147947447</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02512093382197651</v>
+        <v>0.02516544464309807</v>
       </c>
       <c r="K16" t="n">
-        <v>0.09875267801190611</v>
+        <v>0.09884650069562316</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.02048501507770963</v>
+        <v>-0.02021263180460268</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04482032185244989</v>
+        <v>0.04499624628803417</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0969912360908857</v>
+        <v>-0.09685945936205609</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02442690568377385</v>
+        <v>0.02436793672088812</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2297601709127048</v>
+        <v>-0.2297624931360494</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1805220605678049</v>
+        <v>0.1805837815442344</v>
       </c>
       <c r="S16" t="n">
-        <v>0.06539019918805192</v>
+        <v>0.06564257379468544</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1196806309237513</v>
+        <v>-0.1196041718124579</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.121013702613527</v>
+        <v>-0.1208917745650582</v>
       </c>
       <c r="V16" t="n">
-        <v>0.07352881549618651</v>
+        <v>0.073341146269239</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.1477389942032213</v>
+        <v>-0.1476434093567191</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1885037227884333</v>
+        <v>-0.1886401562162983</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.02571166915429595</v>
+        <v>0.0258566502900591</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.144720371180138</v>
+        <v>-0.1445989451180498</v>
       </c>
     </row>
     <row r="17">
@@ -1792,79 +1797,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.09229611290953836</v>
+        <v>-0.09224998874572861</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.00259726437915491</v>
+        <v>-0.002644862395630107</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2290504599163902</v>
+        <v>-0.2290359807126941</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2370600078840905</v>
+        <v>-0.2371891918293908</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01166121713375814</v>
+        <v>0.01160623807879198</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1302022701901307</v>
+        <v>-0.1302699230529848</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1506692403582256</v>
+        <v>0.1505886103787175</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.248639424163533</v>
+        <v>-0.2487714727323843</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1606194040448648</v>
+        <v>-0.1606085487321036</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3373929604986302</v>
+        <v>-0.3375463480306599</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.07935677426868894</v>
+        <v>-0.0794935523760925</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2090905507869948</v>
+        <v>-0.2091357058975058</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1614593559348005</v>
+        <v>0.1612837181202157</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1310600885132061</v>
+        <v>-0.1312150757848662</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2297601709127048</v>
+        <v>-0.2297624931360494</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.02132057702559045</v>
+        <v>-0.02135044584380081</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.001457222863801021</v>
+        <v>-0.001395135280873245</v>
       </c>
       <c r="T17" t="n">
-        <v>0.04819557115209713</v>
+        <v>0.04799680326850316</v>
       </c>
       <c r="U17" t="n">
-        <v>0.06226732750739462</v>
+        <v>0.06216215536815349</v>
       </c>
       <c r="V17" t="n">
-        <v>0.03651733382936487</v>
+        <v>0.036406324768181</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2214118750618214</v>
+        <v>0.2213299353346826</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1194845717643521</v>
+        <v>0.1192925352811003</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1387971717871822</v>
+        <v>0.1387673815714721</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.09153471787459187</v>
+        <v>0.09140226306214673</v>
       </c>
     </row>
     <row r="18">
@@ -1874,79 +1879,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.008435647691230104</v>
+        <v>-0.008282372257091787</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1104820763083747</v>
+        <v>0.1107720591942073</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03803121092501166</v>
+        <v>0.03821744555058555</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06307329270376287</v>
+        <v>0.06304620136505577</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1239776190046461</v>
+        <v>-0.1238802224644606</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.01508649441504894</v>
+        <v>-0.01498647469971973</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1148889428773899</v>
+        <v>0.1149626442191978</v>
       </c>
       <c r="I18" t="n">
-        <v>0.147933598397444</v>
+        <v>0.1478805327113187</v>
       </c>
       <c r="J18" t="n">
-        <v>0.007713302303347485</v>
+        <v>0.008053252466191858</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0615513167349947</v>
+        <v>-0.06149676501353601</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2079473370306356</v>
+        <v>-0.2079328079425145</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.09474841304816356</v>
+        <v>-0.09463613250876128</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1341805013091428</v>
+        <v>-0.1342267186319498</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2505971458399764</v>
+        <v>-0.2506507994936982</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1805220605678049</v>
+        <v>0.1805837815442344</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.02132057702559045</v>
+        <v>-0.02135044584380081</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.04194842875696587</v>
+        <v>0.04207392225726819</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1032616531976678</v>
+        <v>-0.1033384574986124</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08774024536446048</v>
+        <v>-0.0876915768435957</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3056653492611916</v>
+        <v>-0.3055336099721406</v>
       </c>
       <c r="W18" t="n">
-        <v>0.05385592449346091</v>
+        <v>0.05392403326348238</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2189523434491235</v>
+        <v>-0.2190977868826968</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.1284997660818371</v>
+        <v>-0.1284470626219402</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.002792999159357042</v>
+        <v>0.002840759779274969</v>
       </c>
     </row>
     <row r="19">
@@ -1956,79 +1961,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.1099393592129134</v>
+        <v>-0.1096715402491431</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1054225989844731</v>
+        <v>-0.1052337186098929</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1783518011128031</v>
+        <v>-0.1780676468105002</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1084445375635542</v>
+        <v>-0.1082296766706399</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1135929484735063</v>
+        <v>0.1138170852663261</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.08425234243548027</v>
+        <v>-0.08402961110812916</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.09453958322058627</v>
+        <v>-0.09433269685077221</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1387276208899552</v>
+        <v>-0.1386805205858133</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1063450937332363</v>
+        <v>0.1064627469181827</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1298613853834337</v>
+        <v>-0.1296773898151519</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1328373091667853</v>
+        <v>-0.1326199575791063</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.05847751416331348</v>
+        <v>-0.05825850648067452</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.06156876208388055</v>
+        <v>-0.06140207725824862</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1386911605195124</v>
+        <v>-0.1386052563586558</v>
       </c>
       <c r="P19" t="n">
-        <v>0.06539019918805192</v>
+        <v>0.06564257379468544</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.001457222863801021</v>
+        <v>-0.001395135280873245</v>
       </c>
       <c r="R19" t="n">
-        <v>0.04194842875696587</v>
+        <v>0.04207392225726819</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.03189566032313899</v>
+        <v>-0.03173409438146748</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1503737622966565</v>
+        <v>-0.1502128770380784</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.09708867501580438</v>
+        <v>-0.09705389355690723</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.01911639892295898</v>
+        <v>-0.01894808823331165</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2271853656349436</v>
+        <v>-0.2271698145385975</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1799570809055521</v>
+        <v>0.1800540148714439</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.06874098870558139</v>
+        <v>0.0689627869472472</v>
       </c>
     </row>
     <row r="20">
@@ -2038,79 +2043,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.05275985455131184</v>
+        <v>0.05281633063282301</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.03974232060633429</v>
+        <v>-0.03987673975086971</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005835388156302787</v>
+        <v>0.005797567310872284</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1373159993283392</v>
+        <v>-0.1374622607875093</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2627726131735462</v>
+        <v>0.2628065100181004</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2616675098037464</v>
+        <v>-0.2617800037487998</v>
       </c>
       <c r="H20" t="n">
-        <v>0.006579521704376482</v>
+        <v>0.006483902477425836</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5030065483139712</v>
+        <v>0.5028918980575215</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1889990524636923</v>
+        <v>-0.1889946715056594</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01912205896620874</v>
+        <v>-0.01931290046390944</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1571888366462373</v>
+        <v>-0.1573142788404364</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3071277002230445</v>
+        <v>-0.3071695651052038</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4662533462034805</v>
+        <v>0.4661020457396655</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1938716374911583</v>
+        <v>0.1936456512416965</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1196806309237513</v>
+        <v>-0.1196041718124579</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.04819557115209713</v>
+        <v>0.04799680326850316</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.1032616531976678</v>
+        <v>-0.1033384574986124</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.03189566032313899</v>
+        <v>-0.03173409438146748</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3081981186504554</v>
+        <v>-0.3084104206877546</v>
       </c>
       <c r="V20" t="n">
-        <v>0.06026253499386124</v>
+        <v>0.06004159402216473</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.06980167618256135</v>
+        <v>-0.07002409694406329</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.05738130270545511</v>
+        <v>-0.05778345953499508</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.07803171669993274</v>
+        <v>-0.07801929167487116</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.3504390291967195</v>
+        <v>0.3502002146687511</v>
       </c>
     </row>
     <row r="21">
@@ -2120,79 +2125,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.06899215378430569</v>
+        <v>-0.06886692138681517</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01444777548706275</v>
+        <v>0.01430813878914821</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2372610620173846</v>
+        <v>0.2372418219446282</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1456343934665265</v>
+        <v>0.145607480166091</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1038252833343932</v>
+        <v>-0.1037206975247468</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2298892423020111</v>
+        <v>0.2298962810852762</v>
       </c>
       <c r="H21" t="n">
-        <v>0.04820173804353547</v>
+        <v>0.04818628998717302</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2040858827077455</v>
+        <v>-0.2041843373497768</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.06602709281384164</v>
+        <v>-0.06600846246255264</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1663619096213954</v>
+        <v>-0.1664411450377694</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06607480655853307</v>
+        <v>0.06603910002484312</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1338208307639991</v>
+        <v>-0.133827675350275</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.07012080581278801</v>
+        <v>-0.07026386430840173</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.06292308932809113</v>
+        <v>-0.06307131369245933</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.121013702613527</v>
+        <v>-0.1208917745650582</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.06226732750739462</v>
+        <v>0.06216215536815349</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.08774024536446048</v>
+        <v>-0.0876915768435957</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1503737622966565</v>
+        <v>-0.1502128770380784</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3081981186504554</v>
+        <v>-0.3084104206877546</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.09588522406507557</v>
+        <v>-0.09615475220435178</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.03252212245960553</v>
+        <v>-0.03256719372731864</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0005482096142204127</v>
+        <v>0.0002922711488776017</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.2275036741274429</v>
+        <v>-0.2274795201865216</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.08148896525563432</v>
+        <v>0.08143990845729988</v>
       </c>
     </row>
     <row r="22">
@@ -2202,79 +2207,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.2497331904516358</v>
+        <v>-0.2497818373938261</v>
       </c>
       <c r="C22" t="n">
-        <v>0.004246921385941589</v>
+        <v>0.003606276771926022</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.199072024706051</v>
+        <v>-0.1991722757839579</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1467850101407392</v>
+        <v>-0.1470353716451896</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07778865401586069</v>
+        <v>0.07772040980555681</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1121858428987182</v>
+        <v>-0.1124404061729649</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0002515138532249115</v>
+        <v>-0.0004700889859805831</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0301381636938453</v>
+        <v>0.03006124644510077</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1309218495581397</v>
+        <v>-0.1312299214321575</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1119572119076825</v>
+        <v>0.1117532079143059</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05859633738897414</v>
+        <v>0.05839299594341828</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.09372874860603495</v>
+        <v>-0.09393684307138966</v>
       </c>
       <c r="N22" t="n">
-        <v>0.07201465038179668</v>
+        <v>0.07178292317710309</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01119262976974705</v>
+        <v>0.01088845802165236</v>
       </c>
       <c r="P22" t="n">
-        <v>0.07352881549618651</v>
+        <v>0.073341146269239</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.03651733382936487</v>
+        <v>0.036406324768181</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.3056653492611916</v>
+        <v>-0.3055336099721406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.09708867501580438</v>
+        <v>-0.09705389355690723</v>
       </c>
       <c r="T22" t="n">
-        <v>0.06026253499386124</v>
+        <v>0.06004159402216473</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09588522406507557</v>
+        <v>-0.09615475220435178</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.03009841410355285</v>
+        <v>0.02998042176811889</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1205841735625358</v>
+        <v>-0.1209977202707804</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.06473860277375831</v>
+        <v>0.06486465069939744</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.04416189791860232</v>
+        <v>-0.04441784120482568</v>
       </c>
     </row>
     <row r="23">
@@ -2284,79 +2289,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.03609610089577297</v>
+        <v>-0.03593007392508196</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.2918728359673</v>
+        <v>-0.2919197559882994</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07168007094762976</v>
+        <v>0.07179449692296166</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1800348144684367</v>
+        <v>-0.1801279545630484</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1314658902774542</v>
+        <v>-0.1314095280503499</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1346242616124491</v>
+        <v>-0.1345922733239165</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2074226366947533</v>
+        <v>0.207420181396017</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2294846313766877</v>
+        <v>-0.2296271658011686</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2668837030410903</v>
+        <v>-0.2667814048004511</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.004700357538873538</v>
+        <v>-0.004751986596468862</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.20804940814984</v>
+        <v>-0.2081303098943921</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.09646348322619602</v>
+        <v>-0.09640080403981131</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3327715338028381</v>
+        <v>-0.3329886446960995</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1742537132925413</v>
+        <v>-0.1743977761574571</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1477389942032213</v>
+        <v>-0.1476434093567191</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2214118750618214</v>
+        <v>0.2213299353346826</v>
       </c>
       <c r="R23" t="n">
-        <v>0.05385592449346091</v>
+        <v>0.05392403326348238</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.01911639892295898</v>
+        <v>-0.01894808823331165</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.06980167618256135</v>
+        <v>-0.07002409694406329</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.03252212245960553</v>
+        <v>-0.03256719372731864</v>
       </c>
       <c r="V23" t="n">
-        <v>0.03009841410355285</v>
+        <v>0.02998042176811889</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1778194876612362</v>
+        <v>0.1776249340593172</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.3027281388938418</v>
+        <v>0.3027681719895581</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.0557005350054055</v>
+        <v>0.05562784048903453</v>
       </c>
     </row>
     <row r="24">
@@ -2366,79 +2371,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1090711350753841</v>
+        <v>-0.1091277153935969</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1391301071715389</v>
+        <v>-0.139477044620162</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04991668391211933</v>
+        <v>0.04971448542820379</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1671956975777919</v>
+        <v>0.1669845237159357</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.08532098464272159</v>
+        <v>-0.08545690892035933</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1195664543163452</v>
+        <v>0.1193872172447245</v>
       </c>
       <c r="H24" t="n">
-        <v>0.111124016508586</v>
+        <v>0.1109223096010071</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2888588128617268</v>
+        <v>-0.2891012929506928</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1979854045222275</v>
+        <v>-0.1981196967950597</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.06894626734859351</v>
+        <v>-0.06924541095982775</v>
       </c>
       <c r="L24" t="n">
-        <v>0.008982313006026133</v>
+        <v>0.00872265517362595</v>
       </c>
       <c r="M24" t="n">
-        <v>0.00480595699651474</v>
+        <v>0.004603166181255202</v>
       </c>
       <c r="N24" t="n">
-        <v>0.02586050107867468</v>
+        <v>0.02549074894260714</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2133304784340256</v>
+        <v>0.2131093137364903</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1885037227884333</v>
+        <v>-0.1886401562162983</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1194845717643521</v>
+        <v>0.1192925352811003</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.2189523434491235</v>
+        <v>-0.2190977868826968</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2271853656349436</v>
+        <v>-0.2271698145385975</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.05738130270545511</v>
+        <v>-0.05778345953499508</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0005482096142204127</v>
+        <v>0.0002922711488776017</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1205841735625358</v>
+        <v>-0.1209977202707804</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1778194876612362</v>
+        <v>0.1776249340593172</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.1035244472869968</v>
+        <v>-0.1036474844784324</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.2251380951982971</v>
+        <v>-0.225530873074203</v>
       </c>
     </row>
     <row r="25">
@@ -2448,79 +2453,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.08619089730852096</v>
+        <v>-0.08605117210947102</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.202192722114527</v>
+        <v>-0.2020494251346904</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01292970439118614</v>
+        <v>0.01305238654124091</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1482396919697317</v>
+        <v>-0.1481410871798134</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.09580606191283773</v>
+        <v>-0.09564656721368495</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2820732308707531</v>
+        <v>-0.2819706479157542</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.03099954659904147</v>
+        <v>-0.03093110006872712</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1720368923075383</v>
+        <v>-0.1720480937019976</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.04218775799190306</v>
+        <v>-0.04200067933560697</v>
       </c>
       <c r="K25" t="n">
-        <v>0.07019380674236816</v>
+        <v>0.07023693466241687</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1816849017478241</v>
+        <v>-0.1815966141572318</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1089591576588941</v>
+        <v>-0.1088783445811544</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1154139003323497</v>
+        <v>-0.115403743209584</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.117410069678652</v>
+        <v>-0.1174551260344697</v>
       </c>
       <c r="P25" t="n">
-        <v>0.02571166915429595</v>
+        <v>0.0258566502900591</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1387971717871822</v>
+        <v>0.1387673815714721</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.1284997660818371</v>
+        <v>-0.1284470626219402</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1799570809055521</v>
+        <v>0.1800540148714439</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.07803171669993274</v>
+        <v>-0.07801929167487116</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2275036741274429</v>
+        <v>-0.2274795201865216</v>
       </c>
       <c r="V25" t="n">
-        <v>0.06473860277375831</v>
+        <v>0.06486465069939744</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3027281388938418</v>
+        <v>0.3027681719895581</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1035244472869968</v>
+        <v>-0.1036474844784324</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.1487248295655268</v>
+        <v>-0.1486685253886348</v>
       </c>
     </row>
     <row r="26">
@@ -2530,76 +2535,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.08887005473386682</v>
+        <v>0.08902700383944064</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.08247819890793236</v>
+        <v>-0.08257131505284818</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01175241885203644</v>
+        <v>0.01183035744128412</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1762175828669527</v>
+        <v>-0.1763710927566982</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1356286229025384</v>
+        <v>-0.1355731716879831</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0762132241433276</v>
+        <v>-0.076194565823632</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.08442215372258249</v>
+        <v>-0.0844352615849611</v>
       </c>
       <c r="I26" t="n">
-        <v>0.326143800154486</v>
+        <v>0.3259749648975535</v>
       </c>
       <c r="J26" t="n">
-        <v>0.06544180406989297</v>
+        <v>0.06551259929629835</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1205309805052715</v>
+        <v>-0.1206372420352425</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.1984844848751004</v>
+        <v>-0.1986007863816881</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.220650463279321</v>
+        <v>-0.220593990499291</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.02449975751638415</v>
+        <v>-0.02475705210275715</v>
       </c>
       <c r="O26" t="n">
-        <v>0.001705873514255443</v>
+        <v>0.001503559656886216</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.144720371180138</v>
+        <v>-0.1445989451180498</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.09153471787459187</v>
+        <v>0.09140226306214673</v>
       </c>
       <c r="R26" t="n">
-        <v>0.002792999159357042</v>
+        <v>0.002840759779274969</v>
       </c>
       <c r="S26" t="n">
-        <v>0.06874098870558139</v>
+        <v>0.0689627869472472</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3504390291967195</v>
+        <v>0.3502002146687511</v>
       </c>
       <c r="U26" t="n">
-        <v>0.08148896525563432</v>
+        <v>0.08143990845729988</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.04416189791860232</v>
+        <v>-0.04441784120482568</v>
       </c>
       <c r="W26" t="n">
-        <v>0.0557005350054055</v>
+        <v>0.05562784048903453</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.2251380951982971</v>
+        <v>-0.225530873074203</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.1487248295655268</v>
+        <v>-0.1486685253886348</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
